--- a/Data/Regression Evidence 2025/Workday_NewHire_Belgium_Regression_PK17.xlsx
+++ b/Data/Regression Evidence 2025/Workday_NewHire_Belgium_Regression_PK17.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{86A3BC99-28AB-49B0-B7EE-7954F4973467}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{D5B9D598-BF94-4A2A-A535-00BAB08DF576}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -238,10 +238,10 @@
     <t>Mr</t>
   </si>
   <si>
-    <t>Heaven</t>
-  </si>
-  <si>
-    <t>Kuhic</t>
+    <t>Owen</t>
+  </si>
+  <si>
+    <t>Treutel</t>
   </si>
   <si>
     <t>Landline</t>
@@ -379,13 +379,13 @@
     <t>Mme</t>
   </si>
   <si>
-    <t>Ellen</t>
-  </si>
-  <si>
-    <t>Ullrich</t>
-  </si>
-  <si>
-    <t>Auto 61050772</t>
+    <t>Marty</t>
+  </si>
+  <si>
+    <t>Herman</t>
+  </si>
+  <si>
+    <t>Auto 92719870</t>
   </si>
   <si>
     <t>Fixed Term (Fixed Term)</t>
@@ -508,7 +508,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -605,7 +605,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -638,7 +638,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -704,9 +704,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1270,9 +1267,9 @@
         <v>65</v>
       </c>
       <c r="B2" s="12">
-        <v>10700237</v>
-      </c>
-      <c r="C2" s="36" t="s">
+        <v>10700445</v>
+      </c>
+      <c r="C2" s="12" t="s">
         <v>128</v>
       </c>
       <c r="D2" s="13" t="s">
@@ -1301,7 +1298,7 @@
       </c>
       <c r="L2" s="19">
         <f t="shared" ref="L2" ca="1" si="0">TODAY()-31</f>
-        <v>45822</v>
+        <v>45843</v>
       </c>
       <c r="M2" s="14" t="s">
         <v>67</v>
@@ -1335,7 +1332,7 @@
       </c>
       <c r="W2" s="23">
         <f t="shared" ref="W2" ca="1" si="1">L2</f>
-        <v>45822</v>
+        <v>45843</v>
       </c>
       <c r="X2" s="18" t="s">
         <v>78</v>
@@ -1387,7 +1384,7 @@
       </c>
       <c r="AN2" s="29">
         <f t="array" aca="1" ref="AN2:AN3" ca="1">_xlfn.RANDARRAY(2,1,12345678901,99999999999,TRUE)</f>
-        <v>37334631995</v>
+        <v>20515822241</v>
       </c>
       <c r="AO2" s="14" t="s">
         <v>91</v>
@@ -1480,9 +1477,9 @@
         <v>113</v>
       </c>
       <c r="B3" s="12">
-        <v>10700238</v>
-      </c>
-      <c r="C3" s="36" t="s">
+        <v>10700446</v>
+      </c>
+      <c r="C3" s="12" t="s">
         <v>128</v>
       </c>
       <c r="D3" s="13" t="s">
@@ -1511,7 +1508,7 @@
       </c>
       <c r="L3" s="19">
         <f t="shared" ref="L3" ca="1" si="2">TODAY()-31</f>
-        <v>45822</v>
+        <v>45843</v>
       </c>
       <c r="M3" s="14" t="s">
         <v>67</v>
@@ -1545,7 +1542,7 @@
       </c>
       <c r="W3" s="23">
         <f t="shared" ref="W3" ca="1" si="3">L3</f>
-        <v>45822</v>
+        <v>45843</v>
       </c>
       <c r="X3" s="18" t="s">
         <v>78</v>
@@ -1579,7 +1576,7 @@
       </c>
       <c r="AH3" s="19">
         <f ca="1">TODAY()+365</f>
-        <v>46218</v>
+        <v>46239</v>
       </c>
       <c r="AI3" s="18" t="s">
         <v>87</v>
@@ -1598,7 +1595,7 @@
       </c>
       <c r="AN3" s="29">
         <f ca="1"/>
-        <v>39157317735</v>
+        <v>46487309803</v>
       </c>
       <c r="AO3" s="14" t="s">
         <v>91</v>
@@ -1611,7 +1608,7 @@
       </c>
       <c r="AR3" s="19">
         <f t="shared" ref="AR3" ca="1" si="4">AH3</f>
-        <v>46218</v>
+        <v>46239</v>
       </c>
       <c r="AS3" t="s">
         <v>123</v>
